--- a/data/themes/ballets/ballets.xlsx
+++ b/data/themes/ballets/ballets.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ballets" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ballets" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:D101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,6 +432,11 @@
           <t>title</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>only_list</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -507,6 +512,9 @@
           <t>Жизель</t>
         </is>
       </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -537,6 +545,9 @@
           <t>Чёрт на четверых</t>
         </is>
       </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -552,6 +563,9 @@
           <t>Коппелия</t>
         </is>
       </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -597,6 +611,9 @@
           <t>Баядерка</t>
         </is>
       </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -612,6 +629,9 @@
           <t>Камарго</t>
         </is>
       </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -642,6 +662,9 @@
           <t>Пахита</t>
         </is>
       </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -672,6 +695,9 @@
           <t>Дочь фараона</t>
         </is>
       </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -717,6 +743,9 @@
           <t>Арлекинада</t>
         </is>
       </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -747,6 +776,9 @@
           <t>Фея кукол</t>
         </is>
       </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -762,6 +794,9 @@
           <t>Сильфида</t>
         </is>
       </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -777,6 +812,9 @@
           <t>Шопениана</t>
         </is>
       </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -807,6 +845,9 @@
           <t>Манон</t>
         </is>
       </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -822,6 +863,9 @@
           <t>Майерлинг</t>
         </is>
       </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -837,6 +881,9 @@
           <t>Тщетная предосторожность</t>
         </is>
       </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -852,6 +899,9 @@
           <t>Творения Прометея</t>
         </is>
       </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -867,6 +917,9 @@
           <t>Безделушки</t>
         </is>
       </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -942,6 +995,9 @@
           <t>Свадебка</t>
         </is>
       </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -957,6 +1013,9 @@
           <t>Пульчинелла</t>
         </is>
       </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -972,6 +1031,9 @@
           <t>Аполлон Мусагет</t>
         </is>
       </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -987,6 +1049,9 @@
           <t>Поцелуй феи</t>
         </is>
       </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1032,6 +1097,9 @@
           <t>Агон</t>
         </is>
       </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1077,6 +1145,9 @@
           <t>Видение розы</t>
         </is>
       </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1092,6 +1163,9 @@
           <t>Половецкие пляски</t>
         </is>
       </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1152,6 +1226,9 @@
           <t>Дафнис и Хлоя</t>
         </is>
       </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1167,6 +1244,9 @@
           <t>Моя матушка-гусыня</t>
         </is>
       </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1212,6 +1292,9 @@
           <t>Послеполуденный отдых фавна</t>
         </is>
       </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1257,6 +1340,9 @@
           <t>Треуголка</t>
         </is>
       </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1272,6 +1358,9 @@
           <t>Любовь-волшебница</t>
         </is>
       </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1287,6 +1376,9 @@
           <t>Деревянный принц</t>
         </is>
       </c>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1302,6 +1394,9 @@
           <t>Чудесный мандарин</t>
         </is>
       </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1332,6 +1427,9 @@
           <t>Лани</t>
         </is>
       </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1347,6 +1445,9 @@
           <t>Легенда об Иосифе</t>
         </is>
       </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1362,6 +1463,9 @@
           <t>Взбитые сливки</t>
         </is>
       </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1392,6 +1496,9 @@
           <t>Ундина</t>
         </is>
       </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1407,6 +1514,9 @@
           <t>Принц пагод</t>
         </is>
       </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1437,6 +1547,9 @@
           <t>Весна в Аппалачах</t>
         </is>
       </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1452,6 +1565,9 @@
           <t>Билли Кид</t>
         </is>
       </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1467,6 +1583,9 @@
           <t>Фэнси Фри</t>
         </is>
       </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1482,6 +1601,9 @@
           <t>Парижское веселье</t>
         </is>
       </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1512,6 +1634,9 @@
           <t>Зимняя сказка</t>
         </is>
       </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1557,6 +1682,9 @@
           <t>Каменный цветок</t>
         </is>
       </c>
+      <c r="D76" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1572,6 +1700,9 @@
           <t>Блудный сын</t>
         </is>
       </c>
+      <c r="D77" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1587,6 +1718,9 @@
           <t>Стальной скок</t>
         </is>
       </c>
+      <c r="D78" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1617,6 +1751,9 @@
           <t>Гаянэ</t>
         </is>
       </c>
+      <c r="D80" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1647,6 +1784,9 @@
           <t>Бахчисарайский фонтан</t>
         </is>
       </c>
+      <c r="D82" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1662,6 +1802,9 @@
           <t>Пламя Парижа</t>
         </is>
       </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1692,6 +1835,9 @@
           <t>Красный мак</t>
         </is>
       </c>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1722,6 +1868,9 @@
           <t>Золотой век</t>
         </is>
       </c>
+      <c r="D87" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1752,6 +1901,9 @@
           <t>Светлый ручей</t>
         </is>
       </c>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1782,6 +1934,9 @@
           <t>Кармен-сюита</t>
         </is>
       </c>
+      <c r="D91" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1827,6 +1982,9 @@
           <t>Дама с собачкой</t>
         </is>
       </c>
+      <c r="D94" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1857,6 +2015,9 @@
           <t>Анюта</t>
         </is>
       </c>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1872,6 +2033,9 @@
           <t>Ангара</t>
         </is>
       </c>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1887,6 +2051,9 @@
           <t>Семь красавиц</t>
         </is>
       </c>
+      <c r="D98" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1902,6 +2069,9 @@
           <t>Тропою грома</t>
         </is>
       </c>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1916,6 +2086,9 @@
         <is>
           <t>Любовью за любовь</t>
         </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="101">
